--- a/Codebooks/Human Codebooks/content - cleaned/B - Content Analysis Codebook (cleaned) - Auriyana.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/B - Content Analysis Codebook (cleaned) - Auriyana.xlsx
@@ -677,7 +677,7 @@
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Gender Issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
@@ -704,13 +704,13 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>No applicable</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Men's Behavior / Status pressure</t>
+          <t>Men's behavior, / Status pressure</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
@@ -722,18 +722,18 @@
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Commentary/opinion</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>Social interaction</t>
+          <t>Connection/social interaction</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>Social observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X2" s="3" t="inlineStr"/>
@@ -796,13 +796,13 @@
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Socializing, Family, and Gender norms in the household</t>
+          <t>Friends/socializing, Family/children, and Gender norms in the household</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Conversational Content</t>
+          <t>Interview/conversational content</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>No applicable</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr"/>
@@ -847,7 +847,7 @@
       <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>Self Expression</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
@@ -915,13 +915,13 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Marriage and Gender Issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Conversational Content</t>
+          <t>Interview/conversational content</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr"/>
@@ -942,36 +942,36 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>No applicable</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Nigerian Social and Cultural Problems</t>
+          <t>Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>More emotional growth and healing in both parties of a marriage</t>
+          <t>More emotional growth/healing</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Advice / Commentary / Opinion</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Self Expression</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>Cultural Observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Marriage</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>No applicable</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>No problem is identified</t>
+          <t>No clear problem is identified</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -1075,13 +1075,13 @@
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Commentary/opinion</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>Social interaction</t>
+          <t>Connection/social interaction</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
@@ -1149,13 +1149,13 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Family and Religion</t>
+          <t>Family/children, Religion/morality</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Conversational Content</t>
+          <t>Interview/conversational content</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>No applicable</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr"/>
@@ -1194,18 +1194,18 @@
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Advice / Commentary / Opinion</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr"/>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>Identity construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>Religious claims</t>
+          <t>Moral/religious claims</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr"/>
@@ -1268,7 +1268,7 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Gender Issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
@@ -1299,13 +1299,13 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>No applicable</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Global social issue of the patriarchy in particular</t>
+          <t>Global political/social/cultural problems</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -1323,7 +1323,7 @@
       <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Social interaction</t>
+          <t>Connection/social interaction</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -1391,7 +1391,7 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Mental Health amongst men</t>
+          <t>Mental health, amongst men</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>Men need to know they're allowed to be emotionally open</t>
+          <t>Men need to be emotionally open</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr"/>
@@ -1436,18 +1436,18 @@
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Advice / Commentary / Opinion</t>
+          <t>Advice/instruction, Commentary/opinion</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>Identity construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>Social observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
@@ -1510,13 +1510,13 @@
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Religion and Morality</t>
+          <t>Religion/morality</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Self-help content</t>
+          <t>Motivational/self-help content</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -1565,18 +1565,18 @@
       <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>Identity construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>Religious claims</t>
+          <t>Moral/religious claims</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>Anectdotal Exmaples / Religous Refrences</t>
+          <t>Anecdotal examples, References religion/tradition</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>As a man it’s so bl00dy hard to be vulnerable knowing how any lil perceived weakness makes u an even bigger target! I’ve decided I’ll rather go down fighting external wars than die slowly from a silent battle with the enemy within… so help me God #3WorkingDays https://t.co/K58FV1JM72</t>
+          <t>As a man it's so bl00dy hard to be vulnerable knowing how any lil perceived weakness makes u an even bigger target! I've decided I'll rather go down fighting external wars than die slowly from a silent battle with the enemy within… so help me God #3WorkingDays https://t.co/K58FV1JM72</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1633,13 +1633,13 @@
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Mental Health amongst men</t>
+          <t>Mental health, amongst men</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr"/>
@@ -1662,13 +1662,13 @@
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Mental Health and Emotional Struggle</t>
+          <t>Mental health/emotional struggle</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr"/>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>More emotional growth</t>
+          <t>More emotional growth/healing</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>Identity construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
@@ -1748,13 +1748,13 @@
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Gemder issues and family (Parenting)</t>
+          <t>Gender issues, e.g. equality, Family/children</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
@@ -1795,12 +1795,12 @@
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Identity construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>Social observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
@@ -1863,13 +1863,13 @@
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Gender Issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
@@ -1910,12 +1910,12 @@
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>Identity construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about men and women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
@@ -1978,13 +1978,13 @@
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Family and Children</t>
+          <t>Family/children</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
@@ -2085,13 +2085,13 @@
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Marriage and Gender Issues</t>
+          <t>Dating/marriage, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
@@ -2114,7 +2114,7 @@
       <c r="O14" s="3" t="inlineStr"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Nigerian Cultural Problems</t>
+          <t>Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr"/>
@@ -2132,18 +2132,18 @@
       <c r="U14" s="3" t="inlineStr"/>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>Identity construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>Moral / Religous Claims</t>
+          <t>Moral/religious claims</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>Refrences Religion</t>
+          <t>References religion/tradition</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr"/>
@@ -2200,13 +2200,13 @@
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Gender Issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
@@ -2229,7 +2229,7 @@
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>Nigerian Cultural Problems</t>
+          <t>Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr"/>
@@ -2321,7 +2321,7 @@
       <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
@@ -2422,13 +2422,13 @@
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr"/>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
@@ -2529,13 +2529,13 @@
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Dating / Sex</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
@@ -2558,13 +2558,13 @@
       <c r="O18" s="3" t="inlineStr"/>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>More respect for men</t>
+          <t>More equality/respect for men</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr"/>
@@ -2644,13 +2644,13 @@
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Dating / Sex</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr"/>
@@ -2669,13 +2669,13 @@
       <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr"/>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>More respect for men</t>
+          <t>More equality/respect for men</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
@@ -2755,13 +2755,13 @@
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Dating / Sex</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Reaction Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr"/>
@@ -2776,7 +2776,7 @@
       <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>No problem is identified</t>
+          <t>No clear problem is identified</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr"/>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>Generalization about relationships</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr"/>
@@ -2862,13 +2862,13 @@
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Gender Issues / Morality</t>
+          <t>Gender issues, e.g. equality, Religion/morality</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
       <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>Men's Behavior/ Nigerian Culture Problems</t>
+          <t>Men's behavior, / Nigerian Culture Problems</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr"/>
@@ -2909,12 +2909,12 @@
       <c r="U21" s="3" t="inlineStr"/>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>Self Expression</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>Social observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr"/>
@@ -2977,13 +2977,13 @@
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Dating / Sex</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
@@ -3006,7 +3006,7 @@
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr"/>
@@ -3024,12 +3024,12 @@
       <c r="U22" s="3" t="inlineStr"/>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>Self Expression</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>Social observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
@@ -3092,13 +3092,13 @@
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
@@ -3199,13 +3199,13 @@
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Dating / Sex</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
@@ -3220,7 +3220,7 @@
       <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr"/>
@@ -3306,13 +3306,13 @@
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
@@ -3421,13 +3421,13 @@
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Morality</t>
+          <t>Religion/morality</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr"/>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
@@ -3442,7 +3442,7 @@
       <c r="O26" s="3" t="inlineStr"/>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>Social observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr"/>
@@ -3534,7 +3534,7 @@
       <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
@@ -3549,7 +3549,7 @@
       <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>Nigerian Culture Problems</t>
+          <t>Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr"/>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>Social observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr"/>
@@ -3635,13 +3635,13 @@
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr"/>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
       <c r="O28" s="3" t="inlineStr"/>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>Women's Behavior / Men's Behavior</t>
+          <t>Men's behavior, Women's Behavior /</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr"/>
@@ -3746,13 +3746,13 @@
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -3775,7 +3775,7 @@
       <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>Women &amp; Men's Behavior / Nigerian Culture</t>
+          <t>Men's behavior, Women &amp;  |  / Nigerian Culture</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>Social observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr"/>
@@ -3861,13 +3861,13 @@
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
@@ -3882,7 +3882,7 @@
       <c r="O30" s="3" t="inlineStr"/>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>Social observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr"/>
@@ -3968,13 +3968,13 @@
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
@@ -3989,7 +3989,7 @@
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
@@ -4001,7 +4001,7 @@
       <c r="S31" s="3" t="inlineStr"/>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>Personal Story / Commentary</t>
+          <t>Personal story, Commentary/opinion</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr"/>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>Personal Experience / Story about a man</t>
+          <t>Personal experience, / Story about a man</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr"/>
@@ -4075,13 +4075,13 @@
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
@@ -4102,13 +4102,13 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Mixed/unclear</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>Women and Men's Behavior</t>
+          <t>Men's behavior, Women/feminism</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr"/>
@@ -4126,7 +4126,7 @@
       <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>Social Interaction</t>
+          <t>Connection/social interaction</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
@@ -4194,13 +4194,13 @@
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Dating / Sex</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -4221,13 +4221,13 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Mixed/unclear</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr"/>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>Women and Men's Behavior</t>
+          <t>Men's behavior, Women/feminism</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>Social Observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr"/>
@@ -4313,13 +4313,13 @@
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Mental Health amongst men / Gender Issues</t>
+          <t>Mental health, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr"/>
@@ -4334,7 +4334,7 @@
       <c r="O34" s="3" t="inlineStr"/>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>Men's Behavior / Nigerian Culture Issues</t>
+          <t>Men's behavior, / Nigerian Culture Issues</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr"/>
@@ -4357,13 +4357,13 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>Personal Experience / Social Observations</t>
+          <t>Personal experience, Cultural/social observations</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr"/>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>Anecdotal Exmaples</t>
+          <t>Anecdotal examples</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
@@ -4420,13 +4420,13 @@
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>Social Observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr"/>
@@ -4527,13 +4527,13 @@
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Dating / Sex</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr"/>
@@ -4548,7 +4548,7 @@
       <c r="O36" s="3" t="inlineStr"/>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>Women and Men's Behavior</t>
+          <t>Men's behavior, Women/feminism</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>Personal Experience / Social Observations</t>
+          <t>Personal experience, Cultural/social observations</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr"/>
@@ -4640,7 +4640,7 @@
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
@@ -4661,13 +4661,13 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Mixed/unclear</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr"/>
@@ -4679,13 +4679,13 @@
       <c r="S37" s="3" t="inlineStr"/>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>Commentary / Debate</t>
+          <t>Commentary/opinion, Debate/argument</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr"/>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>Self Expression</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -4753,13 +4753,13 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Children / Family / Gender Issues</t>
+          <t>Family/children, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr"/>
@@ -4786,7 +4786,7 @@
       <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>Commentary / Debate</t>
+          <t>Commentary/opinion, Debate/argument</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr"/>
@@ -4860,13 +4860,13 @@
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Gender Issues / Marriage</t>
+          <t>Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
@@ -4887,19 +4887,19 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Mixed/unclear</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>Nigerian Social &amp; Culture Issues</t>
+          <t>Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr"/>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>More emotional growth for both partners in marriage</t>
+          <t>More emotional growth/healing</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -4911,7 +4911,7 @@
       <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -4979,13 +4979,13 @@
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Gender Issues / Dating</t>
+          <t>Gender issues, e.g. equality, Dating/marriage</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
@@ -5000,7 +5000,7 @@
       <c r="O40" s="3" t="inlineStr"/>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>Nigerian Culture Issues</t>
+          <t>Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr"/>
@@ -5012,7 +5012,7 @@
       <c r="S40" s="3" t="inlineStr"/>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>Opinion</t>
+          <t>Commentary/opinion</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr"/>
@@ -5086,13 +5086,13 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Family / Gender Issues</t>
+          <t>Family/children, Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
@@ -5113,13 +5113,13 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>Unlclear</t>
+          <t>Mixed/unclear</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>Nigerian Culture and Social Issues</t>
+          <t>Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr"/>
@@ -5137,7 +5137,7 @@
       <c r="U41" s="3" t="inlineStr"/>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -5427,7 +5427,7 @@
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Commentary / Conversational Content</t>
+          <t>Commentary/reaction content, Interview/conversational content</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
@@ -5450,7 +5450,7 @@
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
@@ -5542,7 +5542,7 @@
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Commentary / Conversational Content</t>
+          <t>Commentary/reaction content, Interview/conversational content</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
@@ -5565,7 +5565,7 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -5577,13 +5577,13 @@
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Commentary</t>
+          <t>Commentary/opinion</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
@@ -5651,13 +5651,13 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Mental Health &amp; Gender Issues</t>
+          <t>Mental health, &amp; Gender Issues</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Commentary / Conversational Content</t>
+          <t>Commentary/reaction content, Interview/conversational content</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr"/>
@@ -5678,13 +5678,13 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Men need to be more emotionally open and heal</t>
+          <t>Men need to be emotionally open</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr"/>
@@ -5696,13 +5696,13 @@
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Commentary / Motivational Speech</t>
+          <t>Motivational speech, Commentary/opinion</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -5776,7 +5776,7 @@
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Commentary / Conversational Content</t>
+          <t>Commentary/reaction content, Interview/conversational content</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
@@ -5791,7 +5791,7 @@
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -5809,7 +5809,7 @@
       <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
@@ -5877,13 +5877,13 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Money/status, Family, &amp; Mental Health</t>
+          <t>Mental health, Money/status, Family/children, &amp;</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Commentary / Conversational Content</t>
+          <t>Commentary/reaction content, Interview/conversational content</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
@@ -5898,7 +5898,7 @@
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr"/>
@@ -5984,13 +5984,13 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Corruption / Family Trauma</t>
+          <t>Social issues, e.g. corruption, Family/children</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Commentary / Conversational Content</t>
+          <t>Commentary/reaction content, Interview/conversational content</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr"/>
@@ -6005,7 +6005,7 @@
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -6091,13 +6091,13 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Family / Mental Health</t>
+          <t>Mental health, Family /</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Commentary / Self-help Content</t>
+          <t>Commentary/reaction content, Motivational/self-help content</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr"/>
@@ -6112,7 +6112,7 @@
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Kenyan Social &amp; Cultural Problems</t>
+          <t>Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr"/>
@@ -6124,13 +6124,13 @@
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Commentary / Motivational Speech</t>
+          <t>Motivational speech, Commentary/opinion</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
@@ -6198,13 +6198,13 @@
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Gender Issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -6227,7 +6227,7 @@
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr"/>
@@ -6239,13 +6239,13 @@
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Conversational Content</t>
+          <t>Personal story</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
@@ -6313,13 +6313,13 @@
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Gender Issues</t>
+          <t>Mental health, / Gender Issues</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr"/>
@@ -6340,13 +6340,13 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>Men need to be more emotionally open and heal</t>
+          <t>Men need to be emotionally open</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr"/>
@@ -6358,13 +6358,13 @@
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/opinion</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
@@ -6438,7 +6438,7 @@
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
@@ -6459,13 +6459,13 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>Men need to be more emotionally open and heal</t>
+          <t>Men need to be emotionally open</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr"/>
@@ -6477,13 +6477,13 @@
       <c r="S11" s="3" t="inlineStr"/>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content / Motivational Speech</t>
+          <t>Motivational speech, Commentary/opinion</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
@@ -6551,13 +6551,13 @@
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Family/children</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Conversational Content</t>
+          <t>Interview/conversational content</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
@@ -6572,7 +6572,7 @@
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr"/>
@@ -6584,13 +6584,13 @@
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Conversational Content</t>
+          <t>Personal story</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
@@ -6658,13 +6658,13 @@
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Trauma</t>
+          <t>Mental health, / Trauma</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Conversational Content</t>
+          <t>Interview/conversational content</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
@@ -6679,7 +6679,7 @@
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr"/>
@@ -6691,13 +6691,13 @@
       <c r="S13" s="3" t="inlineStr"/>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>Conversational Content</t>
+          <t>Personal story</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
@@ -6765,13 +6765,13 @@
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Social Issues / Corruption</t>
+          <t>Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
@@ -6786,7 +6786,7 @@
       <c r="O14" s="3" t="inlineStr"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr"/>
@@ -6872,13 +6872,13 @@
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Family / Social Issues</t>
+          <t>Family/children, Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
@@ -6901,7 +6901,7 @@
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr"/>
@@ -6987,13 +6987,13 @@
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Social Issues / Corruption</t>
+          <t>Social issues, e.g. corruption</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
@@ -7008,7 +7008,7 @@
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr"/>
@@ -7094,13 +7094,13 @@
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Gender Issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Conversational Content</t>
+          <t>Interview/conversational content</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
@@ -7121,13 +7121,13 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Men need to be more emotionally open and heal</t>
+          <t>Men need to be emotionally open</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr"/>
@@ -7139,13 +7139,13 @@
       <c r="S17" s="3" t="inlineStr"/>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/opinion</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr"/>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>Identity Construction</t>
+          <t>Self expression/identity construction</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
@@ -7213,13 +7213,13 @@
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Dating / Sex</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
@@ -7234,7 +7234,7 @@
       <c r="O18" s="3" t="inlineStr"/>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr"/>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr"/>
@@ -7320,13 +7320,13 @@
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Gender Issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr"/>
@@ -7349,7 +7349,7 @@
       <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr"/>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
@@ -7441,7 +7441,7 @@
       <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr"/>
@@ -7464,7 +7464,7 @@
       <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr"/>
@@ -7556,7 +7556,7 @@
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
@@ -7579,7 +7579,7 @@
       <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr"/>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr"/>
@@ -7671,7 +7671,7 @@
       <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
@@ -7694,7 +7694,7 @@
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr"/>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
@@ -7786,7 +7786,7 @@
       <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
@@ -7809,7 +7809,7 @@
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr"/>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr"/>
@@ -7901,7 +7901,7 @@
       <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
@@ -7924,7 +7924,7 @@
       <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr"/>
@@ -8016,7 +8016,7 @@
       <c r="H25" s="3" t="inlineStr"/>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
@@ -8135,7 +8135,7 @@
       <c r="H26" s="3" t="inlineStr"/>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
@@ -8158,7 +8158,7 @@
       <c r="O26" s="3" t="inlineStr"/>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr"/>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr"/>
@@ -8258,7 +8258,7 @@
       <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
@@ -8279,13 +8279,13 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Mixed, Not to date "Born Again" women</t>
+          <t>Mixed/unclear, Other</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr"/>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr"/>
@@ -8377,7 +8377,7 @@
       <c r="H28" s="3" t="inlineStr"/>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
@@ -8400,7 +8400,7 @@
       <c r="O28" s="3" t="inlineStr"/>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr"/>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr"/>
@@ -8492,7 +8492,7 @@
       <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
@@ -8515,7 +8515,7 @@
       <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr"/>
@@ -8607,7 +8607,7 @@
       <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       <c r="O30" s="3" t="inlineStr"/>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr"/>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr"/>
@@ -8722,7 +8722,7 @@
       <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
@@ -8745,7 +8745,7 @@
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr"/>
@@ -8837,7 +8837,7 @@
       <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
@@ -8858,13 +8858,13 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>Men need to be dominate / lead more</t>
+          <t>Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr"/>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr"/>
@@ -8956,7 +8956,7 @@
       <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -8977,13 +8977,13 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>Men need to be dominate / lead more</t>
+          <t>Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr"/>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr"/>
@@ -9075,7 +9075,7 @@
       <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/reaction content</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr"/>
@@ -9098,7 +9098,7 @@
       <c r="O34" s="3" t="inlineStr"/>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       <c r="S34" s="3" t="inlineStr"/>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/opinion</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr"/>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>Social Observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr"/>
@@ -9184,7 +9184,7 @@
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Family</t>
+          <t>Mental health, / Family</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
@@ -9205,7 +9205,7 @@
       <c r="O35" s="3" t="inlineStr"/>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr"/>
@@ -9217,7 +9217,7 @@
       <c r="S35" s="3" t="inlineStr"/>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/opinion</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr"/>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>Social Observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr"/>
@@ -9291,7 +9291,7 @@
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Gender Issues</t>
+          <t>Gender issues, e.g. equality</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
@@ -9314,13 +9314,13 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>Men need to be more emotionally open and heal</t>
+          <t>Men need to be emotionally open</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr"/>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr"/>
@@ -9332,18 +9332,18 @@
       <c r="S36" s="3" t="inlineStr"/>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/opinion</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t>Connection / Self-expression</t>
+          <t>Connection/social interaction, Self expression/identity construction</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>Social Observations</t>
+          <t>Cultural/social observations</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr"/>
@@ -9429,13 +9429,13 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>Men need to be dominate / lead more</t>
+          <t>Men need to dominate/lead</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr"/>
@@ -9447,7 +9447,7 @@
       <c r="S37" s="3" t="inlineStr"/>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/opinion</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr"/>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
@@ -9521,7 +9521,7 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       <c r="O38" s="3" t="inlineStr"/>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr"/>
@@ -9649,7 +9649,7 @@
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Kenyan Cultural Problems</t>
+          <t>Mental health/emotional struggle, Kenyan or Nigerian political/social problems</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr"/>
@@ -9667,7 +9667,7 @@
       <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>Connection / Self-expression</t>
+          <t>Connection/social interaction, Self expression/identity construction</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -9735,7 +9735,7 @@
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Dating/marriage</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
@@ -9760,7 +9760,7 @@
       <c r="O40" s="3" t="inlineStr"/>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>Women / Women's Behavior</t>
+          <t>Women/feminism</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr"/>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>Generalizations about women</t>
+          <t>Generalizations about men/women</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr"/>
@@ -9846,7 +9846,7 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Mental Health / Trauma</t>
+          <t>Mental health, / Trauma</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
@@ -9867,7 +9867,7 @@
       <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>Mental Health</t>
+          <t>Mental health/emotional struggle</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr"/>
@@ -9879,7 +9879,7 @@
       <c r="S41" s="3" t="inlineStr"/>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>Commentary Content</t>
+          <t>Commentary/opinion</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr"/>

--- a/Codebooks/Human Codebooks/content - cleaned/B - Content Analysis Codebook (cleaned) - Auriyana.xlsx
+++ b/Codebooks/Human Codebooks/content - cleaned/B - Content Analysis Codebook (cleaned) - Auriyana.xlsx
@@ -450,42 +450,42 @@
   <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Content ID</t>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Personal experience, / Social Observations</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr"/>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>Personal experience, Cultural/social observations</t>
+          <t>Personal experience, / Social Observations</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr"/>
@@ -5194,42 +5194,42 @@
   <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="26" max="26"/>
+    <col width="26" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="48" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Content ID</t>
